--- a/RFL.xlsx
+++ b/RFL.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D08806A-1840-4C71-8D21-C05294B8A7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516ECAFC-2BF5-487C-9F8E-D997A34EE2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6610" yWindow="2750" windowWidth="22360" windowHeight="16580" xr2:uid="{E0485071-92A8-4146-84EE-E6D3FABA3574}"/>
+    <workbookView xWindow="4180" yWindow="4180" windowWidth="20170" windowHeight="14480" activeTab="1" xr2:uid="{E0485071-92A8-4146-84EE-E6D3FABA3574}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Main" sheetId="1" r:id="rId1"/>
+    <sheet name="Trappsol" sheetId="2" r:id="rId2"/>
+    <sheet name="Niemann Pick C" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="64">
   <si>
     <t>Price</t>
   </si>
@@ -72,13 +74,172 @@
   </si>
   <si>
     <t>Indication</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Generic</t>
+  </si>
+  <si>
+    <t>'Trappsol Cyclo</t>
+  </si>
+  <si>
+    <t>Niemann Pick C</t>
+  </si>
+  <si>
+    <t>Niemann-Pick disease type C. Marie Vanier. Orphanet J Rare Dis 2010</t>
+  </si>
+  <si>
+    <t>Hepatomegaly</t>
+  </si>
+  <si>
+    <t>Sphingomyelin storage in reticuloendothelial and parenchymal tissue</t>
+  </si>
+  <si>
+    <t>Type A: severe, early CNS deterioration, massive visceral and cerebral sphingomyelin storage</t>
+  </si>
+  <si>
+    <t>Type B: chronic course, no nervous system involvement</t>
+  </si>
+  <si>
+    <t>Type C/D: subacute nervous system involvement, moderate and slower progression</t>
+  </si>
+  <si>
+    <t>Type C became a cholesterol storage disorder involving not only endocytosed cholesterol</t>
+  </si>
+  <si>
+    <t>Sequestration of unesterified cholesterol in lysosomes and late endosomes</t>
+  </si>
+  <si>
+    <t>NPC1/NPC2 genes identified; mysterious function, probably involves cholesterol transport</t>
+  </si>
+  <si>
+    <t>Brady found acid sphingomyelinase deficiency (SMPD1 mutations) in A/B but not C/D</t>
+  </si>
+  <si>
+    <t>Autosomal recessive, 0.66-0.83/100,000 births. 0.35-2.20 also reported.</t>
+  </si>
+  <si>
+    <t>onset includes perinatal age to old age</t>
+  </si>
+  <si>
+    <t>lifespan includes a few days to old age</t>
+  </si>
+  <si>
+    <t>majority die between 10 and 25 years of age</t>
+  </si>
+  <si>
+    <t>neurovisceral condition</t>
+  </si>
+  <si>
+    <t>liver, spleen, lung</t>
+  </si>
+  <si>
+    <t>miglustat</t>
+  </si>
+  <si>
+    <t>In the brain, the primary stored lipids are gangliosides</t>
+  </si>
+  <si>
+    <t>ataxia, dysarthria, dysphagia, dementia, VSGP (ventricular supranuclear gaze palsy)</t>
+  </si>
+  <si>
+    <t>Clinical Trials</t>
+  </si>
+  <si>
+    <t>Phase I/II "CTD-TCNCP-201"</t>
+  </si>
+  <si>
+    <t>hydroxypropyl beta cyclodextrin, 2-hydroxypropyl-β-cyclodextrin</t>
+  </si>
+  <si>
+    <t>no placebo, 1500mg/kg or 2500mg/kg IV q2w</t>
+  </si>
+  <si>
+    <t>1 dropout and 2 hearling loss dropouts</t>
+  </si>
+  <si>
+    <t>n=6 1500</t>
+  </si>
+  <si>
+    <t>OLE NCT03893071</t>
+  </si>
+  <si>
+    <t>Chemistry</t>
+  </si>
+  <si>
+    <t>hydrophilic exterior, lipophilic core</t>
+  </si>
+  <si>
+    <t>Phase I n=13 - UCSF site only - Mol Genet Metab 2022 - NCT02939547</t>
+  </si>
+  <si>
+    <t>patients must not have had 17D-NPC-CSS &gt; 30</t>
+  </si>
+  <si>
+    <t>Enrollment began 10/2017, completed 2/2020</t>
+  </si>
+  <si>
+    <t>n=7 2500mg/kg, 3 dropped out? 5/7 had hearing loss</t>
+  </si>
+  <si>
+    <t>2h T1/2, no dose-dependent AUC, CMAX 2mg/ml-2.5mg/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  around 10% ended up in CSF: 40-50ug/ml</t>
+  </si>
+  <si>
+    <t>strong filipin staining</t>
+  </si>
+  <si>
+    <t>but no change in plasma lathosterol or 4beta-hydroxycholesterol</t>
+  </si>
+  <si>
+    <t>in low-dose liver size INCREASED from 16.88cm to 17.55cm, spleen decreased 16.42 to 16.33cm</t>
+  </si>
+  <si>
+    <t>in high-dose liver size decreased from 17.34 to 17.18cm, spleen decreased from 14.94cm to 13.50cm</t>
+  </si>
+  <si>
+    <t>symptoms decreased from 15.2 to 14.8 (4.83) in low dose</t>
+  </si>
+  <si>
+    <t>symptoms INCREASED from 17.7 to 19.8 (6.34) in high dose</t>
+  </si>
+  <si>
+    <t>NCT02912793?</t>
+  </si>
+  <si>
+    <t>interim analysis was not met, p=0.025</t>
+  </si>
+  <si>
+    <t>only p=0.025 of alpha left</t>
+  </si>
+  <si>
+    <t>80% power for 0.7 4D/5D-NPC-SS</t>
+  </si>
+  <si>
+    <t>NCT02534844</t>
+  </si>
+  <si>
+    <t>NCT02612129</t>
+  </si>
+  <si>
+    <t>score is 0-25</t>
+  </si>
+  <si>
+    <t>Phase III "TCNCP-301" n=93</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +253,47 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Ariaarrow"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Ariaarrow"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Ariaarrow"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -101,7 +303,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -109,11 +311,98 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -121,9 +410,24 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -457,20 +761,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE746A9E-5F88-47DC-A3F5-6A3D168D54E2}">
   <dimension ref="B2:N9"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="4.08984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="40.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:14">
+      <c r="B2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="12" t="s">
         <v>10</v>
       </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="13"/>
       <c r="L2" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,13 +785,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14">
       <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="F3" s="6"/>
       <c r="L3" s="1" t="s">
         <v>1</v>
       </c>
@@ -496,7 +804,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14">
+      <c r="B4" s="7"/>
+      <c r="F4" s="6"/>
       <c r="L4" s="1" t="s">
         <v>3</v>
       </c>
@@ -506,7 +816,9 @@
       </c>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14">
+      <c r="B5" s="7"/>
+      <c r="F5" s="6"/>
       <c r="L5" s="1" t="s">
         <v>4</v>
       </c>
@@ -517,7 +829,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
       <c r="L6" s="1" t="s">
         <v>5</v>
       </c>
@@ -528,7 +845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14">
       <c r="L7" s="1" t="s">
         <v>6</v>
       </c>
@@ -537,7 +854,7 @@
         <v>73.502992000000006</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14">
       <c r="M9" s="1">
         <f>+M5/M3</f>
         <v>0.58648081434467803</v>
@@ -546,4 +863,305 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C5EFD6-D69B-4931-8318-639C9C959C32}">
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
+  <cols>
+    <col min="1" max="1" width="4.7265625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="B2" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="B3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="B4" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="13">
+      <c r="C7" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="C8" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="C9" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="C10" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="C11" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="13">
+      <c r="C13" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="C14" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" ht="13">
+      <c r="C20" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{B389E044-EB72-4153-AB2F-B1D7834F8DCF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA6EBA3-5BC8-4E4A-B35C-FBE373C4DE99}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
+  <cols>
+    <col min="1" max="1" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.7265625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="13">
+      <c r="B2" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="13">
+      <c r="B4" s="18"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="C13" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="C14" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="C17" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="C18" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="D19" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="C21" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{23C1F00A-DD8A-4C8E-B19E-B46DDFE4EA2E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>